--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -6055,7 +6055,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>136917695</v>
       </c>
       <c r="B43" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136917699</v>
       </c>
       <c r="B44" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>136917683</v>
       </c>
       <c r="B45" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>136917686</v>
       </c>
       <c r="B46" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>136917694</v>
       </c>
       <c r="B47" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>136917747</v>
       </c>
       <c r="B48" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>136917698</v>
       </c>
       <c r="B49" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>136917724</v>
       </c>
       <c r="B50" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>136917726</v>
       </c>
       <c r="B51" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>136917732</v>
       </c>
       <c r="B52" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>136917741</v>
       </c>
       <c r="B53" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>136917695</v>
       </c>
       <c r="B43" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136917699</v>
       </c>
       <c r="B44" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>136917683</v>
       </c>
       <c r="B45" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>136917686</v>
       </c>
       <c r="B46" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>136917694</v>
       </c>
       <c r="B47" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>136917747</v>
       </c>
       <c r="B48" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>136917698</v>
       </c>
       <c r="B49" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>136917724</v>
       </c>
       <c r="B50" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>136917726</v>
       </c>
       <c r="B51" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>136917732</v>
       </c>
       <c r="B52" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>136917741</v>
       </c>
       <c r="B53" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -4895,11 +4895,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vallhall, Hjd</t>
@@ -5002,11 +4998,7 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vallhall, Hjd</t>
@@ -5109,11 +5101,7 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vallhall, Hjd</t>
@@ -5221,11 +5209,7 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vallhall, Hjd</t>
@@ -5333,11 +5317,7 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vallhall, Hjd</t>
@@ -5445,11 +5425,7 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vallhall, Hjd</t>
@@ -5557,11 +5533,7 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vallhall, Hjd</t>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>136917695</v>
       </c>
       <c r="B43" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>136917699</v>
       </c>
       <c r="B44" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>136917683</v>
       </c>
       <c r="B45" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>136917686</v>
       </c>
       <c r="B46" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>136917694</v>
       </c>
       <c r="B47" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>136917747</v>
       </c>
       <c r="B48" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136917698</v>
       </c>
       <c r="B49" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>136917724</v>
       </c>
       <c r="B50" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>136917726</v>
       </c>
       <c r="B51" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>136917732</v>
       </c>
       <c r="B52" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>136917741</v>
       </c>
       <c r="B53" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>136917695</v>
       </c>
       <c r="B43" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>136917699</v>
       </c>
       <c r="B44" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>136917683</v>
       </c>
       <c r="B45" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>136917686</v>
       </c>
       <c r="B46" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>136917694</v>
       </c>
       <c r="B47" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>136917747</v>
       </c>
       <c r="B48" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136917698</v>
       </c>
       <c r="B49" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>136917724</v>
       </c>
       <c r="B50" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>136917726</v>
       </c>
       <c r="B51" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>136917732</v>
       </c>
       <c r="B52" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>136917741</v>
       </c>
       <c r="B53" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>136917695</v>
       </c>
       <c r="B43" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>136917699</v>
       </c>
       <c r="B44" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>136917683</v>
       </c>
       <c r="B45" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>136917686</v>
       </c>
       <c r="B46" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>136917694</v>
       </c>
       <c r="B47" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>136917747</v>
       </c>
       <c r="B48" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136917698</v>
       </c>
       <c r="B49" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>136917724</v>
       </c>
       <c r="B50" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>136917726</v>
       </c>
       <c r="B51" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>136917732</v>
       </c>
       <c r="B52" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>136917741</v>
       </c>
       <c r="B53" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 37227-2026 artfynd.xlsx
+++ b/artfynd/A 37227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136917693</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136917711</v>
       </c>
       <c r="B3" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136917718</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136917720</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136917721</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136917723</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136917727</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136917729</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136917736</v>
       </c>
       <c r="B10" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136917738</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136917742</v>
       </c>
       <c r="B12" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136917744</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136917700</v>
       </c>
       <c r="B14" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136917706</v>
       </c>
       <c r="B15" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136917712</v>
       </c>
       <c r="B16" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136917739</v>
       </c>
       <c r="B17" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136917743</v>
       </c>
       <c r="B18" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136917697</v>
       </c>
       <c r="B19" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136917714</v>
       </c>
       <c r="B20" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136917740</v>
       </c>
       <c r="B21" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136917725</v>
       </c>
       <c r="B22" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136917713</v>
       </c>
       <c r="B23" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136917704</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136917733</v>
       </c>
       <c r="B25" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136917684</v>
       </c>
       <c r="B26" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>136917730</v>
       </c>
       <c r="B27" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136917750</v>
       </c>
       <c r="B28" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>136917687</v>
       </c>
       <c r="B29" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136917728</v>
       </c>
       <c r="B30" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>136917734</v>
       </c>
       <c r="B31" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136917691</v>
       </c>
       <c r="B32" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136917710</v>
       </c>
       <c r="B33" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>136917715</v>
       </c>
       <c r="B34" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>136917717</v>
       </c>
       <c r="B35" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136917719</v>
       </c>
       <c r="B36" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136917722</v>
       </c>
       <c r="B37" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>136917737</v>
       </c>
       <c r="B38" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>136917745</v>
       </c>
       <c r="B39" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>136917692</v>
       </c>
       <c r="B40" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>136917707</v>
       </c>
       <c r="B41" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>136917748</v>
       </c>
       <c r="B42" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136917703</v>
       </c>
       <c r="B54" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>136917689</v>
       </c>
       <c r="B55" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>136917716</v>
       </c>
       <c r="B56" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>136917746</v>
       </c>
       <c r="B57" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136917708</v>
       </c>
       <c r="B58" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>136917709</v>
       </c>
       <c r="B59" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
